--- a/data/trans_orig/Q02D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 9,84</t>
+          <t>4,35; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,23</t>
+          <t>4,18; 6,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,35</t>
+          <t>4,74; 8,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,42</t>
+          <t>2,02; 11,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,28</t>
+          <t>6,05; 9,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,94</t>
+          <t>6,44; 8,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,54</t>
+          <t>8,85; 11,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,6</t>
+          <t>5,79; 8,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,21</t>
+          <t>5,88; 7,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,05</t>
+          <t>7,92; 10,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,28</t>
+          <t>3,82; 5,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,16</t>
+          <t>5,18; 6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,88</t>
+          <t>7,01; 9,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,52</t>
+          <t>6,78; 13,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,32</t>
+          <t>6,97; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 8,43</t>
+          <t>7,6; 8,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 10,6</t>
+          <t>9,21; 10,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 11,59</t>
+          <t>8,92; 11,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,08</t>
+          <t>6,03; 7,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,49</t>
+          <t>6,85; 7,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 9,8</t>
+          <t>8,62; 9,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 11,43</t>
+          <t>8,69; 11,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,99</t>
+          <t>3,2; 4,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,15</t>
+          <t>4,49; 5,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,05</t>
+          <t>6,75; 7,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,69</t>
+          <t>5,55; 7,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,03</t>
+          <t>5,04; 6,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,02</t>
+          <t>6,36; 6,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 9,49</t>
+          <t>8,27; 9,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,73</t>
+          <t>7,24; 8,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,04</t>
+          <t>4,31; 5,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,12</t>
+          <t>5,63; 6,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 8,64</t>
+          <t>7,74; 8,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,03</t>
+          <t>6,71; 8,06</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,02</t>
+          <t>2,02; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,44</t>
+          <t>3,56; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,85</t>
+          <t>5,09; 6,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,48</t>
+          <t>3,96; 6,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,92</t>
+          <t>4,2; 5,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,84</t>
+          <t>4,91; 5,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,52</t>
+          <t>6,81; 8,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,62</t>
+          <t>5,42; 7,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,35</t>
+          <t>3,29; 4,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,06</t>
+          <t>4,4; 5,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,45</t>
+          <t>6,27; 7,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,63</t>
+          <t>5,05; 6,67</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,93</t>
+          <t>3,06; 8,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,02</t>
+          <t>4,61; 6,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,06</t>
+          <t>3,49; 6,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,01</t>
+          <t>1,86; 3,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,77</t>
+          <t>4,03; 6,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,65</t>
+          <t>5,01; 6,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,77</t>
+          <t>7,36; 11,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,94</t>
+          <t>4,64; 8,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,56</t>
+          <t>4,17; 6,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,51</t>
+          <t>5,05; 6,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,93</t>
+          <t>6,13; 8,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,02</t>
+          <t>3,63; 7,04</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,43</t>
+          <t>4,31; 7,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,43</t>
+          <t>4,53; 9,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,36</t>
+          <t>4,52; 11,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,25</t>
+          <t>4,58; 8,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,81</t>
+          <t>5,43; 7,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,34</t>
+          <t>4,69; 9,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,96</t>
+          <t>3,18; 4,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,77</t>
+          <t>4,76; 7,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,8</t>
+          <t>5,65; 7,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,58</t>
+          <t>5,15; 8,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,95</t>
+          <t>3,29; 4,85</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,43</t>
+          <t>5,84; 13,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,97</t>
+          <t>4,1; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,86; 8,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,95</t>
+          <t>5,1; 10,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,46</t>
+          <t>5,36; 8,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,74</t>
+          <t>6,2; 11,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,31</t>
+          <t>3,48; 7,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,73</t>
+          <t>5,97; 10,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,65</t>
+          <t>5,39; 7,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,41</t>
+          <t>5,81; 10,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,28</t>
+          <t>2,19; 7,22</t>
         </is>
       </c>
     </row>
@@ -1696,42 +1696,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,33</t>
+          <t>3,65; 4,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,16</t>
+          <t>4,68; 5,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,33</t>
+          <t>6,5; 7,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,34</t>
+          <t>5,48; 7,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 6,55</t>
+          <t>5,87; 6,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,97</t>
+          <t>6,55; 6,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 9,36</t>
+          <t>8,59; 9,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,58</t>
+          <t>7,41; 8,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,4</t>
+          <t>7,84; 8,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,94</t>
+          <t>6,82; 7,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>5,6</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,07</t>
+          <t>4,45; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,23</t>
+          <t>4,22; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,43</t>
+          <t>4,77; 8,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,68</t>
+          <t>2,12; 11,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,26</t>
+          <t>5,91; 9,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,04</t>
+          <t>6,39; 7,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,64</t>
+          <t>8,94; 11,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,66</t>
+          <t>3,79; 10,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,69</t>
+          <t>5,68; 8,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,23</t>
+          <t>5,87; 7,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 10,08</t>
+          <t>7,81; 10,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,12</t>
+          <t>3,77; 8,51</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,19</t>
+          <t>3,85; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 6,19</t>
+          <t>5,18; 6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,1</t>
+          <t>7,04; 8,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,4</t>
+          <t>6,99; 12,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,39</t>
+          <t>7,01; 8,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 8,39</t>
+          <t>7,63; 8,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 10,67</t>
+          <t>9,18; 10,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,57</t>
+          <t>8,99; 11,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,13</t>
+          <t>5,96; 7,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,48</t>
+          <t>6,81; 7,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 9,75</t>
+          <t>8,58; 9,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 11,19</t>
+          <t>8,67; 11,02</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,33</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,04</t>
+          <t>3,17; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,17</t>
+          <t>4,49; 5,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,96</t>
+          <t>6,75; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,95</t>
+          <t>5,35; 7,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,06</t>
+          <t>5,01; 6,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 6,99</t>
+          <t>6,35; 7,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 9,43</t>
+          <t>8,23; 9,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,76</t>
+          <t>7,21; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,05</t>
+          <t>4,33; 5,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,13</t>
+          <t>5,68; 6,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 8,58</t>
+          <t>7,72; 8,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,06</t>
+          <t>6,62; 7,79</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,05</t>
+          <t>2,04; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,46</t>
+          <t>3,56; 4,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,93</t>
+          <t>5,09; 6,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,59</t>
+          <t>4,03; 6,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,85</t>
+          <t>4,2; 5,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,87</t>
+          <t>4,92; 5,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,65</t>
+          <t>6,8; 8,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,6</t>
+          <t>5,54; 7,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,34</t>
+          <t>3,26; 4,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,07</t>
+          <t>4,41; 5,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,5</t>
+          <t>6,3; 7,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,67</t>
+          <t>5,06; 6,54</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,91</t>
+          <t>3,02; 8,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,9</t>
+          <t>4,72; 7,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,04</t>
+          <t>3,4; 6,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,88</t>
+          <t>2,48; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,99</t>
+          <t>4,04; 6,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,7</t>
+          <t>4,91; 6,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,47</t>
+          <t>7,61; 11,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,75</t>
+          <t>4,63; 8,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,56</t>
+          <t>4,11; 6,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,56</t>
+          <t>5,03; 6,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,84</t>
+          <t>6,06; 8,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,04</t>
+          <t>4,06; 6,85</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,94</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,53</t>
+          <t>4,27; 7,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,73</t>
+          <t>4,63; 9,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,45</t>
+          <t>4,55; 11,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,42</t>
+          <t>4,62; 8,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,69</t>
+          <t>5,47; 7,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,61</t>
+          <t>4,78; 9,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,93</t>
+          <t>3,25; 4,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,75</t>
+          <t>4,76; 7,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,84</t>
+          <t>5,58; 7,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,84</t>
+          <t>5,15; 8,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,85</t>
+          <t>3,29; 4,67</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,32</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,92</t>
+          <t>5,64; 14,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,19</t>
+          <t>4,08; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,0</t>
+          <t>2,61; 7,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,47</t>
+          <t>4,97; 10,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,38</t>
+          <t>5,31; 8,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,56</t>
+          <t>6,29; 11,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,91</t>
+          <t>3,48; 8,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,76</t>
+          <t>5,86; 10,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,83</t>
+          <t>5,32; 7,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,28</t>
+          <t>5,79; 10,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,22</t>
+          <t>2,18; 6,89</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,34</t>
+          <t>3,65; 4,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,13</t>
+          <t>4,69; 5,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,29</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,55</t>
+          <t>5,85; 6,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,98</t>
+          <t>6,57; 6,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,59; 9,37</t>
+          <t>8,58; 9,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,69</t>
+          <t>7,42; 8,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,64</t>
+          <t>5,08; 5,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,19</t>
+          <t>5,88; 6,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,44</t>
+          <t>7,86; 8,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,84</t>
+          <t>6,78; 7,74</t>
         </is>
       </c>
     </row>
